--- a/data/exercise.xlsx
+++ b/data/exercise.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daochashao/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daochashao/PycharmProjects/py-st-run-pro/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9134D34-D0AD-644B-9BE8-B7ABF16F237B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F0B744-7CF6-8545-A0FF-B1104B15DD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{EA37398A-F59A-0547-835E-C0FC0B8A539B}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="26">
   <si>
     <t>date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -229,9 +229,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -269,7 +269,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -375,7 +375,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -517,7 +517,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -525,23 +525,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8721549-F49A-B041-ACCD-4DCDC21C0647}">
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -555,14 +555,14 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -579,32 +579,32 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -617,14 +617,14 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="1">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3">
         <v>37.5</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>5.61</v>
-      </c>
-      <c r="F2" s="1">
-        <v>3</v>
       </c>
       <c r="G2" s="1">
         <v>440</v>
@@ -641,32 +641,32 @@
       <c r="K2" s="1">
         <v>152</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="1">
+        <v>6</v>
+      </c>
+      <c r="M2" s="3">
         <v>0.42</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>2.52</v>
       </c>
-      <c r="N2" s="3">
+      <c r="O2" s="3">
         <v>13.18</v>
       </c>
-      <c r="O2" s="3">
+      <c r="P2" s="3">
         <v>21</v>
       </c>
-      <c r="P2" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
         <v>159</v>
       </c>
-      <c r="R2" s="4">
+      <c r="S2" s="4">
         <v>143</v>
       </c>
-      <c r="S2" s="4">
+      <c r="T2" s="4">
         <v>136</v>
-      </c>
-      <c r="T2" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -679,14 +679,14 @@
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="1">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3">
         <v>37.28</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>5.59</v>
-      </c>
-      <c r="F3" s="1">
-        <v>3</v>
       </c>
       <c r="G3" s="1">
         <v>419</v>
@@ -703,17 +703,17 @@
       <c r="K3" s="1">
         <v>150</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="L3" s="1">
+        <v>6</v>
+      </c>
+      <c r="R3" s="4">
         <v>158</v>
       </c>
-      <c r="R3" s="4">
+      <c r="S3" s="4">
         <v>139</v>
       </c>
-      <c r="S3" s="4">
+      <c r="T3" s="4">
         <v>128</v>
-      </c>
-      <c r="T3" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -726,14 +726,14 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
         <v>44.44</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>6.09</v>
-      </c>
-      <c r="F4" s="1">
-        <v>3</v>
       </c>
       <c r="G4" s="1">
         <v>477</v>
@@ -750,32 +750,32 @@
       <c r="K4" s="1">
         <v>148</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="1">
+        <v>6</v>
+      </c>
+      <c r="M4" s="3">
         <v>5.22</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>3.1</v>
       </c>
-      <c r="N4" s="3">
+      <c r="O4" s="3">
         <v>13.59</v>
       </c>
-      <c r="O4" s="3">
+      <c r="P4" s="3">
         <v>22.13</v>
       </c>
-      <c r="P4" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>117</v>
+      <c r="Q4" s="3">
+        <v>0</v>
       </c>
       <c r="R4" s="4">
         <v>117</v>
       </c>
       <c r="S4" s="4">
+        <v>117</v>
+      </c>
+      <c r="T4" s="4">
         <v>110</v>
-      </c>
-      <c r="T4" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -788,14 +788,14 @@
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3">
         <v>37.32</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>5.55</v>
-      </c>
-      <c r="F5" s="1">
-        <v>3</v>
       </c>
       <c r="G5" s="1">
         <v>435</v>
@@ -812,32 +812,32 @@
       <c r="K5" s="1">
         <v>145</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="1">
+        <v>5</v>
+      </c>
+      <c r="M5" s="3">
         <v>1.01</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>2.16</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>31.5</v>
       </c>
-      <c r="O5" s="3">
+      <c r="P5" s="3">
         <v>2.2400000000000002</v>
       </c>
-      <c r="P5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
         <v>149</v>
       </c>
-      <c r="R5" s="4">
+      <c r="S5" s="4">
         <v>125</v>
       </c>
-      <c r="S5" s="4">
+      <c r="T5" s="4">
         <v>120</v>
-      </c>
-      <c r="T5" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -850,14 +850,14 @@
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3">
         <v>37.409999999999997</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>5.53</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3</v>
       </c>
       <c r="G6" s="1">
         <v>432</v>
@@ -874,32 +874,32 @@
       <c r="K6" s="1">
         <v>145</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="1">
+        <v>5</v>
+      </c>
+      <c r="M6" s="3">
         <v>1.22</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>33.04</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
         <v>149</v>
       </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <v>129</v>
       </c>
-      <c r="S6" s="4">
+      <c r="T6" s="4">
         <v>120</v>
-      </c>
-      <c r="T6" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -912,14 +912,14 @@
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3">
         <v>37.49</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>5.68</v>
-      </c>
-      <c r="F7" s="1">
-        <v>4</v>
       </c>
       <c r="G7" s="1">
         <v>446</v>
@@ -936,32 +936,32 @@
       <c r="K7" s="1">
         <v>151</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="1">
+        <v>6</v>
+      </c>
+      <c r="M7" s="3">
         <v>1.1399999999999999</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>1</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>15.19</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="3">
         <v>20.149999999999999</v>
       </c>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4">
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
         <v>155</v>
       </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <v>140</v>
       </c>
-      <c r="S7" s="4">
+      <c r="T7" s="4">
         <v>130</v>
-      </c>
-      <c r="T7" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -974,14 +974,14 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
         <v>42.27</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>5.95</v>
-      </c>
-      <c r="F8" s="1">
-        <v>4</v>
       </c>
       <c r="G8" s="1">
         <v>467</v>
@@ -998,32 +998,32 @@
       <c r="K8" s="1">
         <v>145</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="1">
+        <v>6</v>
+      </c>
+      <c r="M8" s="3">
         <v>3.54</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3.11</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30.28</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4.53</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
         <v>116</v>
       </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <v>118</v>
       </c>
-      <c r="S8" s="4">
+      <c r="T8" s="4">
         <v>117</v>
-      </c>
-      <c r="T8" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1036,14 +1036,14 @@
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
         <v>37.08</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>5.56</v>
-      </c>
-      <c r="F9" s="1">
-        <v>4</v>
       </c>
       <c r="G9" s="1">
         <v>427</v>
@@ -1060,32 +1060,32 @@
       <c r="K9" s="1">
         <v>147</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="1">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>0.59</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2.33</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23.26</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10.1</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4">
         <v>154</v>
       </c>
-      <c r="R9" s="4">
+      <c r="S9" s="4">
         <v>135</v>
       </c>
-      <c r="S9" s="4">
+      <c r="T9" s="4">
         <v>126</v>
-      </c>
-      <c r="T9" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1098,14 +1098,14 @@
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
         <v>37.4</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>5.74</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5</v>
       </c>
       <c r="G10" s="1">
         <v>445</v>
@@ -1122,32 +1122,32 @@
       <c r="K10" s="1">
         <v>156</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="1">
+        <v>7</v>
+      </c>
+      <c r="M10" s="3">
         <v>0.46</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1.1299999999999999</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6.08</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27.36</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1.59</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="R10" s="4">
         <v>163</v>
       </c>
-      <c r="R10" s="4">
+      <c r="S10" s="4">
         <v>151</v>
       </c>
-      <c r="S10" s="4">
+      <c r="T10" s="4">
         <v>139</v>
-      </c>
-      <c r="T10" s="1">
-        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1160,14 +1160,14 @@
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="1">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
         <v>46.32</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>6.32</v>
-      </c>
-      <c r="F11" s="1">
-        <v>5</v>
       </c>
       <c r="G11" s="1">
         <v>524</v>
@@ -1181,23 +1181,23 @@
       <c r="K11" s="1">
         <v>150</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="1">
+        <v>7</v>
+      </c>
+      <c r="M11" s="3">
         <v>6.29</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>1.25</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>6.23</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="3">
         <v>28.4</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>3.28</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>135</v>
       </c>
       <c r="R11" s="4">
         <v>135</v>
@@ -1205,8 +1205,8 @@
       <c r="S11" s="4">
         <v>135</v>
       </c>
-      <c r="T11" s="1">
-        <v>7</v>
+      <c r="T11" s="4">
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1219,14 +1219,14 @@
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
         <v>37.19</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>5.61</v>
-      </c>
-      <c r="F12" s="1">
-        <v>5</v>
       </c>
       <c r="G12" s="1">
         <v>431</v>
@@ -1243,32 +1243,32 @@
       <c r="K12" s="1">
         <v>152</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="1">
+        <v>6</v>
+      </c>
+      <c r="M12" s="3">
         <v>0.51</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1.22</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13.17</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>21.5</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4">
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4">
         <v>157</v>
       </c>
-      <c r="R12" s="4">
+      <c r="S12" s="4">
         <v>137</v>
       </c>
-      <c r="S12" s="4">
+      <c r="T12" s="4">
         <v>125</v>
-      </c>
-      <c r="T12" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1281,14 +1281,14 @@
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="1">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3">
         <v>37.31</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>5.61</v>
-      </c>
-      <c r="F13" s="1">
-        <v>5</v>
       </c>
       <c r="G13" s="1">
         <v>433</v>
@@ -1305,32 +1305,32 @@
       <c r="K13" s="1">
         <v>150</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="1">
+        <v>6</v>
+      </c>
+      <c r="M13" s="3">
         <v>1.02</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>1.21</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>20.170000000000002</v>
       </c>
-      <c r="O13" s="3">
+      <c r="P13" s="3">
         <v>14.51</v>
       </c>
-      <c r="P13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
         <v>154</v>
       </c>
-      <c r="R13" s="4">
+      <c r="S13" s="4">
         <v>138</v>
       </c>
-      <c r="S13" s="4">
+      <c r="T13" s="4">
         <v>128</v>
-      </c>
-      <c r="T13" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1343,14 +1343,14 @@
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="1">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>37.380000000000003</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>5.58</v>
-      </c>
-      <c r="F14" s="1">
-        <v>5</v>
       </c>
       <c r="G14" s="1">
         <v>456</v>
@@ -1367,32 +1367,32 @@
       <c r="K14" s="1">
         <v>151</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="1">
+        <v>6</v>
+      </c>
+      <c r="M14" s="3">
         <v>0.59</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1.28</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16.05</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>19.07</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
         <v>156</v>
       </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <v>136</v>
       </c>
-      <c r="S14" s="4">
+      <c r="T14" s="4">
         <v>129</v>
-      </c>
-      <c r="T14" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1405,14 +1405,14 @@
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3">
         <v>37.19</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>5.56</v>
-      </c>
-      <c r="F15" s="1">
-        <v>5</v>
       </c>
       <c r="G15" s="1">
         <v>448</v>
@@ -1429,32 +1429,32 @@
       <c r="K15" s="1">
         <v>150</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="1">
+        <v>6</v>
+      </c>
+      <c r="M15" s="3">
         <v>1.2</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1.38</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>18.37</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>15.44</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="4">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
         <v>155</v>
       </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <v>138</v>
       </c>
-      <c r="S15" s="4">
+      <c r="T15" s="4">
         <v>126</v>
-      </c>
-      <c r="T15" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1467,14 +1467,14 @@
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="1">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3">
         <v>37.380000000000003</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>5.57</v>
-      </c>
-      <c r="F16" s="1">
-        <v>5</v>
       </c>
       <c r="G16" s="1">
         <v>460</v>
@@ -1491,32 +1491,32 @@
       <c r="K16" s="1">
         <v>151</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="1">
+        <v>6</v>
+      </c>
+      <c r="M16" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>1.57</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>14.49</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>19.41</v>
       </c>
-      <c r="P16" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="4">
+      <c r="Q16" s="3">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
         <v>158</v>
       </c>
-      <c r="R16" s="4">
+      <c r="S16" s="4">
         <v>141</v>
       </c>
-      <c r="S16" s="4">
+      <c r="T16" s="4">
         <v>131</v>
-      </c>
-      <c r="T16" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1529,14 +1529,14 @@
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="1">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
         <v>37.17</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>5.54</v>
-      </c>
-      <c r="F17" s="1">
-        <v>5</v>
       </c>
       <c r="G17" s="1">
         <v>433</v>
@@ -1553,32 +1553,32 @@
       <c r="K17" s="1">
         <v>150</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="1">
+        <v>6</v>
+      </c>
+      <c r="M17" s="3">
         <v>1.06</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2.57</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19.559999999999999</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13.19</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="4">
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4">
         <v>156</v>
       </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <v>139</v>
       </c>
-      <c r="S17" s="4">
+      <c r="T17" s="4">
         <v>128</v>
-      </c>
-      <c r="T17" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1591,14 +1591,14 @@
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
         <v>37.299999999999997</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>5.59</v>
-      </c>
-      <c r="F18" s="1">
-        <v>5</v>
       </c>
       <c r="G18" s="1">
         <v>443</v>
@@ -1615,32 +1615,32 @@
       <c r="K18" s="1">
         <v>153</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="1">
+        <v>6</v>
+      </c>
+      <c r="M18" s="3">
         <v>1.0900000000000001</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>0.44</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9.4</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>25.56</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="4">
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4">
         <v>158</v>
       </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <v>140</v>
       </c>
-      <c r="S18" s="4">
+      <c r="T18" s="4">
         <v>130</v>
-      </c>
-      <c r="T18" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1653,14 +1653,14 @@
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="1">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3">
         <v>37.090000000000003</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>5.64</v>
-      </c>
-      <c r="F19" s="1">
-        <v>5</v>
       </c>
       <c r="G19" s="1">
         <v>425</v>
@@ -1677,32 +1677,32 @@
       <c r="K19" s="1">
         <v>146</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="3">
         <v>0.49</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>3.49</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>28.14</v>
       </c>
-      <c r="O19" s="3">
+      <c r="P19" s="3">
         <v>4.18</v>
       </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="4">
+      <c r="Q19" s="3">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4">
         <v>150</v>
       </c>
-      <c r="R19" s="4">
+      <c r="S19" s="4">
         <v>131</v>
       </c>
-      <c r="S19" s="4">
+      <c r="T19" s="4">
         <v>119</v>
-      </c>
-      <c r="T19" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1715,14 +1715,14 @@
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
         <v>37.299999999999997</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>5.48</v>
-      </c>
-      <c r="F20" s="1">
-        <v>5</v>
       </c>
       <c r="G20" s="1">
         <v>428</v>
@@ -1739,32 +1739,32 @@
       <c r="K20" s="1">
         <v>147</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>1.38</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8.43</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12.17</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14.52</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4">
         <v>155</v>
       </c>
-      <c r="R20" s="4">
+      <c r="S20" s="4">
         <v>135</v>
       </c>
-      <c r="S20" s="4">
+      <c r="T20" s="4">
         <v>128</v>
-      </c>
-      <c r="T20" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -1777,14 +1777,14 @@
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="1">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3">
         <v>37.19</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>5.62</v>
-      </c>
-      <c r="F21" s="1">
-        <v>6</v>
       </c>
       <c r="G21" s="1">
         <v>429</v>
@@ -1801,32 +1801,32 @@
       <c r="K21" s="1">
         <v>151</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="1">
+        <v>6</v>
+      </c>
+      <c r="M21" s="3">
         <v>0.44</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1.45</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19.149999999999999</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15.34</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4">
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4">
         <v>158</v>
       </c>
-      <c r="R21" s="4">
+      <c r="S21" s="4">
         <v>136</v>
       </c>
-      <c r="S21" s="4">
+      <c r="T21" s="4">
         <v>126</v>
-      </c>
-      <c r="T21" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -1839,14 +1839,14 @@
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="1">
+        <v>6</v>
+      </c>
+      <c r="E22" s="3">
         <v>37.200000000000003</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>5.6</v>
-      </c>
-      <c r="F22" s="1">
-        <v>6</v>
       </c>
       <c r="G22" s="1">
         <v>438</v>
@@ -1863,32 +1863,32 @@
       <c r="K22" s="1">
         <v>149</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="1">
+        <v>6</v>
+      </c>
+      <c r="M22" s="3">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2.0299999999999998</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>22.06</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12.14</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="4">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4">
         <v>156</v>
       </c>
-      <c r="R22" s="4">
+      <c r="S22" s="4">
         <v>135</v>
       </c>
-      <c r="S22" s="4">
+      <c r="T22" s="4">
         <v>129</v>
-      </c>
-      <c r="T22" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -1901,14 +1901,14 @@
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="1">
+        <v>6</v>
+      </c>
+      <c r="E23" s="3">
         <v>39.14</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <v>5.72</v>
-      </c>
-      <c r="F23" s="1">
-        <v>6</v>
       </c>
       <c r="G23" s="1">
         <v>494</v>
@@ -1925,32 +1925,32 @@
       <c r="K23" s="1">
         <v>156</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="1">
+        <v>6</v>
+      </c>
+      <c r="M23" s="3">
         <v>0.39</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1.34</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6.2</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>30.28</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>0.13</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="R23" s="4">
         <v>134</v>
       </c>
-      <c r="R23" s="4">
+      <c r="S23" s="4">
         <v>132</v>
       </c>
-      <c r="S23" s="4">
+      <c r="T23" s="4">
         <v>131</v>
-      </c>
-      <c r="T23" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -1963,14 +1963,14 @@
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="1">
+        <v>6</v>
+      </c>
+      <c r="E24" s="3">
         <v>37.22</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>5.43</v>
-      </c>
-      <c r="F24" s="1">
-        <v>6</v>
       </c>
       <c r="G24" s="1">
         <v>420</v>
@@ -1987,32 +1987,32 @@
       <c r="K24" s="1">
         <v>150</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="1">
+        <v>6</v>
+      </c>
+      <c r="M24" s="3">
         <v>0.51</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1.38</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18.43</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="4">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="4">
         <v>154</v>
       </c>
-      <c r="R24" s="4">
+      <c r="S24" s="4">
         <v>148</v>
       </c>
-      <c r="S24" s="4">
+      <c r="T24" s="4">
         <v>134</v>
-      </c>
-      <c r="T24" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2025,14 +2025,14 @@
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="1">
+        <v>6</v>
+      </c>
+      <c r="E25" s="3">
         <v>22.41</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>3.32</v>
-      </c>
-      <c r="F25" s="1">
-        <v>6</v>
       </c>
       <c r="G25" s="1">
         <v>282</v>
@@ -2049,32 +2049,32 @@
       <c r="K25" s="1">
         <v>151</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="1">
+        <v>6</v>
+      </c>
+      <c r="M25" s="3">
         <v>0.53</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="3">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N25" s="3">
+      <c r="O25" s="3">
         <v>9.3699999999999992</v>
       </c>
-      <c r="O25" s="3">
+      <c r="P25" s="3">
         <v>11.15</v>
       </c>
-      <c r="P25" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="4">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="4">
         <v>159</v>
       </c>
-      <c r="R25" s="4">
+      <c r="S25" s="4">
         <v>138</v>
       </c>
-      <c r="S25" s="4">
+      <c r="T25" s="4">
         <v>129</v>
-      </c>
-      <c r="T25" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2087,14 +2087,14 @@
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="1">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3">
         <v>40.01</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>5.71</v>
-      </c>
-      <c r="F26" s="1">
-        <v>6</v>
       </c>
       <c r="G26" s="1">
         <v>434</v>
@@ -2111,32 +2111,32 @@
       <c r="K26" s="1">
         <v>144</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="1">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>2.42</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3.17</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>31.46</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2.16</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4">
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="4">
         <v>120</v>
       </c>
-      <c r="R26" s="4">
+      <c r="S26" s="4">
         <v>118</v>
       </c>
-      <c r="S26" s="4">
+      <c r="T26" s="4">
         <v>115</v>
-      </c>
-      <c r="T26" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2149,14 +2149,14 @@
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="1">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3">
         <v>39.22</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <v>5.6</v>
-      </c>
-      <c r="F27" s="1">
-        <v>6</v>
       </c>
       <c r="G27" s="1">
         <v>430</v>
@@ -2173,32 +2173,32 @@
       <c r="K27" s="1">
         <v>141</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="1">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>2.39</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6.2</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>30.23</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
-      <c r="Q27" s="4">
-        <v>115</v>
+      <c r="Q27" s="3">
+        <v>0</v>
       </c>
       <c r="R27" s="4">
         <v>115</v>
       </c>
       <c r="S27" s="4">
+        <v>115</v>
+      </c>
+      <c r="T27" s="4">
         <v>113</v>
-      </c>
-      <c r="T27" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2211,14 +2211,14 @@
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="1">
+        <v>6</v>
+      </c>
+      <c r="E28" s="3">
         <v>37.08</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <v>5.39</v>
-      </c>
-      <c r="F28" s="1">
-        <v>6</v>
       </c>
       <c r="G28" s="1">
         <v>415</v>
@@ -2235,32 +2235,218 @@
       <c r="K28" s="1">
         <v>147</v>
       </c>
-      <c r="L28" s="3">
+      <c r="L28" s="1">
+        <v>5</v>
+      </c>
+      <c r="M28" s="3">
         <v>1.19</v>
       </c>
-      <c r="M28" s="3">
+      <c r="N28" s="3">
         <v>2.58</v>
       </c>
-      <c r="N28" s="3">
+      <c r="O28" s="3">
         <v>27.2</v>
       </c>
-      <c r="O28" s="3">
+      <c r="P28" s="3">
         <v>5.33</v>
       </c>
-      <c r="P28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="4">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="4">
         <v>151</v>
       </c>
-      <c r="R28" s="4">
+      <c r="S28" s="4">
         <v>132</v>
       </c>
-      <c r="S28" s="4">
+      <c r="T28" s="4">
         <v>122</v>
       </c>
-      <c r="T28" s="1">
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29" s="2">
+        <v>46317.381249999999</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1">
+        <v>6</v>
+      </c>
+      <c r="E29" s="3">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5.48</v>
+      </c>
+      <c r="G29" s="1">
+        <v>413</v>
+      </c>
+      <c r="H29" s="1">
+        <v>484</v>
+      </c>
+      <c r="I29" s="1">
+        <v>164</v>
+      </c>
+      <c r="J29" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="K29" s="1">
+        <v>146</v>
+      </c>
+      <c r="L29" s="1">
         <v>5</v>
+      </c>
+      <c r="M29" s="3">
+        <v>1.07</v>
+      </c>
+      <c r="N29" s="3">
+        <v>3.04</v>
+      </c>
+      <c r="O29" s="3">
+        <v>30.51</v>
+      </c>
+      <c r="P29" s="3">
+        <v>2.29</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4">
+        <v>148</v>
+      </c>
+      <c r="S29" s="4">
+        <v>131</v>
+      </c>
+      <c r="T29" s="4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" s="2">
+        <v>46318.379861111112</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1">
+        <v>6</v>
+      </c>
+      <c r="E30" s="3">
+        <v>37.24</v>
+      </c>
+      <c r="F30" s="1">
+        <v>5.53</v>
+      </c>
+      <c r="G30" s="1">
+        <v>419</v>
+      </c>
+      <c r="H30" s="1">
+        <v>489</v>
+      </c>
+      <c r="I30" s="1">
+        <v>163</v>
+      </c>
+      <c r="J30" s="1">
+        <v>6.46</v>
+      </c>
+      <c r="K30" s="1">
+        <v>144</v>
+      </c>
+      <c r="L30" s="1">
+        <v>5</v>
+      </c>
+      <c r="M30" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="N30" s="3">
+        <v>3.42</v>
+      </c>
+      <c r="O30" s="3">
+        <v>31.56</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="4">
+        <v>150</v>
+      </c>
+      <c r="S30" s="4">
+        <v>130</v>
+      </c>
+      <c r="T30" s="4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31" s="2">
+        <v>46323.394444444442</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1">
+        <v>6</v>
+      </c>
+      <c r="E31" s="3">
+        <v>38.119999999999997</v>
+      </c>
+      <c r="F31" s="1">
+        <v>5.55</v>
+      </c>
+      <c r="G31" s="1">
+        <v>481</v>
+      </c>
+      <c r="H31" s="1">
+        <v>552</v>
+      </c>
+      <c r="I31" s="1">
+        <v>163</v>
+      </c>
+      <c r="J31" s="1">
+        <v>6.53</v>
+      </c>
+      <c r="K31" s="1">
+        <v>145</v>
+      </c>
+      <c r="L31" s="1">
+        <v>5</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="N31" s="3">
+        <v>3.45</v>
+      </c>
+      <c r="O31" s="3">
+        <v>29.53</v>
+      </c>
+      <c r="P31" s="3">
+        <v>3.54</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="4">
+        <v>128</v>
+      </c>
+      <c r="S31" s="4">
+        <v>131</v>
+      </c>
+      <c r="T31" s="4">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
